--- a/docs/PRAP_Programming_Specification_v1.30.xlsx
+++ b/docs/PRAP_Programming_Specification_v1.30.xlsx
@@ -7167,7 +7167,7 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Project PRJ-099 has periods but NOBODY ASSIGNED TO IT, so the application shows no resource for it anywhere except the timeline. Its own standard says it needs 38.05 FTE-months across 24 month(s), from 2025-03, peaking at 1.86 FTE in 2026-10. That demand is real and unallocated: a project-month IS its standard and the people on it divide it (REQ-CAL-19), so having nobody on it does not make the figure nought - it makes it invisible. Assign somebody and the project takes its place in every table and chart, at exactly these figures. This is a note, not a fault: it is the state every project is in until its first assignment, so it never refuses an edit and never questions a save.</t>
+          <t>Project PRJ-099 has periods but NOBODY ASSIGNED TO IT. It is listed in Resource by project and drawn on the timeline, but EVERY ONE OF ITS MONTHS IS EMPTY, and it adds nothing to the demand charts - a row of blanks, which reads as a project that costs nothing rather than one nobody has been put on yet. Its own standard says it needs 38.05 FTE-months across 24 month(s), from 2025-03, peaking at 1.86 FTE in 2026-10. That demand is real and unallocated: a project-month IS its standard and the people on it divide it (REQ-CAL-19), so having nobody on it does not make the figure nought - it leaves it unstated. Assign somebody and the project fills in across every table and chart, at exactly these figures. This is a note, not a fault: it is the state every project is in until its first assignment, so it never refuses an edit and never questions a save.</t>
         </is>
       </c>
     </row>
